--- a/OUT_EXCEL/out_4.xlsx
+++ b/OUT_EXCEL/out_4.xlsx
@@ -449,7 +449,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BANG CAN DOI KE TOAN HOP NHAT</t>
+          <t>BẢNG CÂN ĐỐIKẾ TOÁN HỢP NHẢT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -462,7 +462,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ngay 31 thang 12 nam 2019</t>
+          <t>ngày 31 tháng 12 năm 2019</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -477,7 +477,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Don vi: trieu dong</t>
+          <t>Dơn vị: triểu đỏng</t>
         </is>
       </c>
     </row>
@@ -487,22 +487,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ma so</t>
+          <t>Mã sỗ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TAISAN</t>
+          <t>TẢISẢN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>So cuoi nam</t>
+          <t>Số cuổi nẵm</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>So dau nam</t>
+          <t>Số đầu nẵm</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A.TAISANNGAN HAN</t>
+          <t>A. TẢISẢN NGAN HẠN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -537,22 +537,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>I. Tien va cac khoan turong durong tien</t>
+          <t>L Tỉền và các khoan tuung đuong tiên</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.988.328</t>
+          <t>2988.328</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4.548.432</t>
+          <t>4.548432</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>II. Dau tur tai chinh ngan han</t>
+          <t>IL. Dau tư tài chính ngắn han</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>III. Cac khoan phai thu ngan han.</t>
+          <t>III, Các khoản phảỉ thu ngín hon</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IV. Hang ton kho</t>
+          <t>IV . Hằng ton kho</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>V. Tai san ngan han khac</t>
+          <t>V. Tài san ngản han khác</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B. TAISANDAIHAN</t>
+          <t>B. TÀISẢV DÀlHẠN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>I. Cac khoan phai thu dai han</t>
+          <t>4 Các khoun phi thu dài han</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>II. Tai san co djnh</t>
+          <t>IL Tài san cò dinh</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>III. Bat dong san dau tur</t>
+          <t>III. Bất dậng san dau tu</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IV. Tai san do dang dai han.</t>
+          <t>IV. Tài sẩn dở dang dài han</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>V.Cac khoan dau tur tai chinh dai han</t>
+          <t>V.Các khoẳn dầu tu tài chinh dài hạn</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>260)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VI. Tai san dai han khac</t>
+          <t>VI: Tài san dài han khác</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TONGCONG TAISAN</t>
+          <t>TONG CONG TAISẢN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -862,22 +862,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ma so</t>
+          <t>Mã số</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NGUON VON</t>
+          <t>NGUỎN VỎN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>So cuoi nam</t>
+          <t>Số cuốí nẵm</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>so dau nam</t>
+          <t>Só đẳu nẳtn</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C.NO PHAI TRA</t>
+          <t>C.NỢ PHẴl TRẴ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31.023.040</t>
+          <t>31.023(0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>I. Ng ngan han</t>
+          <t>1 Nợ ngan Ian</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>II. Ng dai han.</t>
+          <t>IL; Nợ dàỉ han</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>D.VON CHU SOHOU</t>
+          <t>D. VMN CHỦ SỞ HIỮU</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>I. Von chu so huu</t>
+          <t>1, Vấn chủ sử hữu</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>II. Nguon kinh phi va quy khac</t>
+          <t>IL. Nguon kinh phi và quỹ  khác</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TONG CONGNGUON VON</t>
+          <t>TONG CONG NGUON VON</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
